--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES I-X/FRACC II/LTAIPT_A63F02A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/4TO_TRIMESTRE/FRACCIONES I-X/FRACC II/LTAIPT_A63F02A.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c8ec10a61716621/Documentos/CUARTO PAG WEB/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_D526ED5AF0BFDC4B82D1BA15982F8A3F833DB259" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{F8F6C148-AB49-4909-A24C-64014B381BEB}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="332">
   <si>
     <t>48947</t>
   </si>
@@ -115,7 +121,7 @@
     <t>Denominación del área</t>
   </si>
   <si>
-    <t>Denominación del puesto</t>
+    <t>Denominación del puesto (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Denominación del cargo (de conformidad con nombramiento otorgado)</t>
@@ -127,10 +133,10 @@
     <t>Denominación de la norma que establece atribuciones, responsabilidades y/o funciones y el fundamento legal (artículo y/o fracción)</t>
   </si>
   <si>
-    <t>Atribuciones, responsabilidades y/o funciones, según sea el caso</t>
-  </si>
-  <si>
-    <t>Hipervínculo al perfil y/o requerimientos del puesto o cargo, en su caso</t>
+    <t>Atribuciones, responsabilidades y/o funciones, según sea el caso (Redactadas con perspectiva de género)</t>
+  </si>
+  <si>
+    <t>Hipervínculo al perfil y/o requerimientos del puesto o cargo, en su caso (Redactados con perspectiva de género)</t>
   </si>
   <si>
     <t>Número total de prestadores de servicios profesionales</t>
@@ -148,559 +154,616 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>47F551990B031A861AD476CAE982BF5D</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>Dirección General</t>
+  </si>
+  <si>
+    <t>Director General</t>
+  </si>
+  <si>
+    <t>Director General del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Junta Directiva - Gobierno del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Reglamento Interior del Organismo Público Desconcentrado del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Artículo 10</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Departamento de Recursos Humanos</t>
+  </si>
+  <si>
+    <t>Director de Area</t>
+  </si>
+  <si>
+    <t>Secretario General del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Ver nota</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel B</t>
+  </si>
+  <si>
+    <t>Subdirector de Plantel B</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativa del Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 12 Santa Cruz</t>
+  </si>
+  <si>
+    <t>Director del Plantel</t>
+  </si>
+  <si>
+    <t>Director del Plantel 12 Santa Cruz</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona III/ Dirección General</t>
+  </si>
+  <si>
+    <t>Artículo 47</t>
+  </si>
+  <si>
+    <t>Subdirección Plantel 12 Santa Cruz</t>
+  </si>
+  <si>
+    <t>Unidad de Control Interno</t>
+  </si>
+  <si>
+    <t>Contralor Interno</t>
+  </si>
+  <si>
+    <t>Contralor Interno del Colegio de Bachilleres del Estado de Tlaxcala</t>
+  </si>
+  <si>
+    <t>Artículo 52</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 23 San Pablo</t>
+  </si>
+  <si>
+    <t>Director del Plantel 23 San Pablo</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona II/ Dirección General</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona III</t>
+  </si>
+  <si>
+    <t>Coordinadora Sectorial</t>
+  </si>
+  <si>
+    <t>Coordinador Sectorial Zona III</t>
+  </si>
+  <si>
+    <t>Artículo 40</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 03 Calpulalpan</t>
+  </si>
+  <si>
+    <t>Director del Plantel 03 Calpulalpan</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona IV</t>
+  </si>
+  <si>
+    <t>Coordinador Sectorial</t>
+  </si>
+  <si>
+    <t>Coordinador Sectorial Zona IV</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Directora del Plantel</t>
+  </si>
+  <si>
+    <t>Director del Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona IV/ Dirección General</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Subdirectora del Plantel</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativo del Plantel 02 Huamantla</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 03 Calpulalpan</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 03 Calpulalpan</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 07 Buenavista</t>
+  </si>
+  <si>
+    <t>Director del Plantel 07 Buenavista</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 09 Tlaxco</t>
+  </si>
+  <si>
+    <t>Director del Plantel 09 Tlaxco</t>
+  </si>
+  <si>
+    <t>Director del Plantel 10 Apizaco</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 17 Cuapiaxtla</t>
+  </si>
+  <si>
+    <t>Director del Plantel 17 Cuapiaxtla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 15 Hueyotlipan</t>
+  </si>
+  <si>
+    <t>Director del Plantel 15 Hueyotlipan</t>
+  </si>
+  <si>
+    <t>Subdirección del Plantel 17 Cuapiaxtla</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 17 Cuapiaxtla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 18 Atltzayanca</t>
+  </si>
+  <si>
+    <t>Director del Plantel 18 Altzayanca</t>
+  </si>
+  <si>
+    <t>Subdirección del Plantel 18 Atltzayanca</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 18 Atltzayanca</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 18 Altzayanca</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 19 Xaloztoc</t>
+  </si>
+  <si>
+    <t>Director del Plantel 19 Xaloztoc</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 19 Xaloztoc</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 19 Xaloztoc</t>
+  </si>
+  <si>
+    <t>Dirección de  Plantel 20 Ixtenco</t>
+  </si>
+  <si>
+    <t>Director del Plantel 20 Ixtenco</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 20 Ixtenco.</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 20 Ixtenco</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 20 Ixtenco</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 24 Tizatlán</t>
+  </si>
+  <si>
+    <t>Director del Plantel 24 Tizatlán</t>
+  </si>
+  <si>
+    <t>Departamento de Información y Relaciones Públicas</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Información y Relaciones Públicas</t>
+  </si>
+  <si>
+    <t>Artículo 19</t>
+  </si>
+  <si>
+    <t>Subdirección Jurídica</t>
+  </si>
+  <si>
+    <t>Subdirector de Área</t>
+  </si>
+  <si>
+    <t>Subdirector Jurídico</t>
+  </si>
+  <si>
+    <t>Artículo 15</t>
+  </si>
+  <si>
+    <t>Departamento Jurídico</t>
+  </si>
+  <si>
+    <t>Jefa de Departamento</t>
+  </si>
+  <si>
+    <t>Jefa de Departamento Jurídico</t>
+  </si>
+  <si>
+    <t>Artículo 16</t>
+  </si>
+  <si>
+    <t>Dirección Académica</t>
+  </si>
+  <si>
+    <t>Directora Académica</t>
+  </si>
+  <si>
+    <t>Artículo 31</t>
+  </si>
+  <si>
+    <t>Subdirección de Planeación y Evaluación Institucional</t>
+  </si>
+  <si>
+    <t>Subdirectora de Área</t>
+  </si>
+  <si>
+    <t>Subdirector de Planeación y Evaluación Institucional</t>
+  </si>
+  <si>
+    <t>Artículo 17</t>
+  </si>
+  <si>
+    <t>Departamento de Planeación y Evaluación Institucional</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Planeación y Evaluación Institucional</t>
+  </si>
+  <si>
+    <t>Artículo 18</t>
+  </si>
+  <si>
+    <t>Subdirección de Seguimiento Académico</t>
+  </si>
+  <si>
+    <t>Subdirector de Seguimiento Académico</t>
+  </si>
+  <si>
+    <t>Artículo 21</t>
+  </si>
+  <si>
+    <t>Jefatura de Materia</t>
+  </si>
+  <si>
+    <t>Jefe de materia</t>
+  </si>
+  <si>
+    <t>Artículo 25</t>
+  </si>
+  <si>
+    <t>Departamento de Bibliotecas y Laboratorio</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Bibliotecas y Laboratorio</t>
+  </si>
+  <si>
+    <t>Artículo 24</t>
+  </si>
+  <si>
+    <t>Departamento de Planes y Programas de Estudio</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Planes y Programas de Estudio</t>
+  </si>
+  <si>
+    <t>Artículo 22</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicios Escolares</t>
+  </si>
+  <si>
+    <t>Subdirector de Servicios Escolares</t>
+  </si>
+  <si>
+    <t>Artículo 26</t>
+  </si>
+  <si>
+    <t>Artículo 27</t>
+  </si>
+  <si>
+    <t>Departamento de Orientación Educativa y Servicio Social</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Orientación Educativca y Servicio Social</t>
+  </si>
+  <si>
+    <t>Subdirección de actividades paraescolares</t>
+  </si>
+  <si>
+    <t>Artículo 29</t>
+  </si>
+  <si>
+    <t>Departamento de actividades deportivas</t>
+  </si>
+  <si>
+    <t>Jefe  de Departamento de actividades deportivas</t>
+  </si>
+  <si>
+    <t>Subdirección de paraescolares</t>
+  </si>
+  <si>
+    <t>Dirección Administrativa</t>
+  </si>
+  <si>
+    <t>Director Administrativo</t>
+  </si>
+  <si>
+    <t>Subdirección Financiera</t>
+  </si>
+  <si>
+    <t>Subdirector Financiero</t>
+  </si>
+  <si>
+    <t>Artículo 36</t>
+  </si>
+  <si>
+    <t>Departamento de Contabilidad</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Contabilidad</t>
+  </si>
+  <si>
+    <t>Artículo 37</t>
+  </si>
+  <si>
+    <t>Departamento de Programación y Presupuesto</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Programación y Presupuesto</t>
+  </si>
+  <si>
+    <t>Artículo 38</t>
+  </si>
+  <si>
+    <t>Subdirector de Servicios Administrativos</t>
+  </si>
+  <si>
+    <t>Artículo 32</t>
+  </si>
+  <si>
+    <t>Departamento de Recursos Materiales y Servicios Generales</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Recursos Materiales y Servicios Generales</t>
+  </si>
+  <si>
+    <t>Subdirección de Servicios Administrativos</t>
+  </si>
+  <si>
+    <t>Artículo 34</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Recursos Humanos</t>
+  </si>
+  <si>
+    <t>Artículo 33</t>
+  </si>
+  <si>
+    <t>Departamento de Inventarios</t>
+  </si>
+  <si>
+    <t>Jefe de Departamento de Inventarios</t>
+  </si>
+  <si>
+    <t>Artículo 35</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona I</t>
+  </si>
+  <si>
+    <t>Coordinador Sectorial Zona I</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 01 Tlaxcala</t>
+  </si>
+  <si>
+    <t>Director del Plantel 01 Tlaxcala</t>
+  </si>
+  <si>
+    <t>Coordinación Sectorial Zona I/ Dirección General</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativo del Plantel 01 Tlaxcala</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativo del Plantel 01 Tlaxcala</t>
   </si>
   <si>
     <t>Subdirección Académica del Plantel 01 Tlaxcala</t>
   </si>
   <si>
-    <t>Subdirector del Plantel</t>
-  </si>
-  <si>
     <t>Subdirector Académico del Plantel 01 Tlaxcala</t>
   </si>
   <si>
-    <t>Dirección del Plantel 01 Tlaxcala</t>
-  </si>
-  <si>
-    <t>Reglamento Interior del Organismo Público Desconcentrado del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Departamento de Recursos Humanos</t>
-  </si>
-  <si>
-    <t>13/01/2023</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de octubre de 2022 al 31 de diciembre de 2022, en el Colegio de Bachilleres del Estado de Tlaxcala, es facultad del Director General  proponer ante la Junta Directiva las candidaturas para ocupar las Direcciones de las unidades administrativas y de los planteles, motivo por el cual no se tiene ninguna norma establecida con los requerimientos del puesto  para cubrir  un perfil Directivo. De igual forma este Colegio de Bachilleres del Estado de Tlaxcala, no cuenta con prestadores de servicios profesionales que formen parte de la estructura orgánica, por lo tanto no hay información que reportar.</t>
-  </si>
-  <si>
-    <t>C56CD8BC21B6CAF5DC348B8C857006FC</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativo del Plantel 01 Tlaxcala</t>
-  </si>
-  <si>
-    <t>Subdirector Administrativo del Plantel 01 Tlaxcala</t>
-  </si>
-  <si>
-    <t>89CA0A09E0B964AA270461338755E44B</t>
-  </si>
-  <si>
-    <t>Director del Plantel</t>
-  </si>
-  <si>
-    <t>Director del Plantel 01 Tlaxcala</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona I/ Dirección General</t>
-  </si>
-  <si>
-    <t>Artículo 47</t>
-  </si>
-  <si>
-    <t>08EDC79AD36F39C3A63252DF1D00BD0E</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona I</t>
-  </si>
-  <si>
-    <t>Coordinador Sectorial</t>
-  </si>
-  <si>
-    <t>Coordinador Sectorial Zona I</t>
-  </si>
-  <si>
-    <t>Dirección General</t>
-  </si>
-  <si>
-    <t>Artículo 40</t>
-  </si>
-  <si>
-    <t>6742884071FDA255D1066C833E2CEED1</t>
-  </si>
-  <si>
-    <t>Departamento de Programación y Presupuesto</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Programación y Presupuesto</t>
-  </si>
-  <si>
-    <t>Subdirección Financiera</t>
-  </si>
-  <si>
-    <t>Artículo 38</t>
-  </si>
-  <si>
-    <t>07FF5EAD21E48341B8BB06C833379E2A</t>
-  </si>
-  <si>
-    <t>Departamento de Contabilidad</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Contabilidad</t>
-  </si>
-  <si>
-    <t>Artículo 37</t>
-  </si>
-  <si>
-    <t>263BBE3441A4537077B5B83987F5DBF7</t>
-  </si>
-  <si>
-    <t>Subdirector de Área</t>
-  </si>
-  <si>
-    <t>Subdirector Financiero</t>
-  </si>
-  <si>
-    <t>Dirección Administrativa</t>
-  </si>
-  <si>
-    <t>Artículo 36</t>
-  </si>
-  <si>
-    <t>05284E966293D5D7C56378FD80E3F03E</t>
-  </si>
-  <si>
-    <t>Departamento de Recursos Materiales y Servicios Generales</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Recursos Materiales y Servicios Generales</t>
-  </si>
-  <si>
-    <t>Subdirección de Servicios Administrativos</t>
-  </si>
-  <si>
-    <t>Artículo 34</t>
-  </si>
-  <si>
-    <t>2C4DC97BB7AB3FA4807636A3716A0679</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 24 Tizatlán</t>
-  </si>
-  <si>
-    <t>Director del Plantel 24 Tizatlán</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona IV/ Dirección General</t>
-  </si>
-  <si>
-    <t>FE36C9E4351E1536E5EF3B71E1064F7E</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativa del Plantel 20 Ixtenco.</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 20 Ixtenco</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 20 Ixtenco</t>
-  </si>
-  <si>
-    <t>CDE20A347EA6CAD2D825318F7F3BCDDB</t>
-  </si>
-  <si>
-    <t>Departamento de Inventarios</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Inventarios</t>
-  </si>
-  <si>
-    <t>Artículo 35</t>
-  </si>
-  <si>
-    <t>9D20E849EAD9BD9DAF9A724FF101E4CB</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Recursos Humanos</t>
-  </si>
-  <si>
-    <t>Artículo 33</t>
-  </si>
-  <si>
-    <t>49F9D8848DAAEF3EF682139B7926C02E</t>
-  </si>
-  <si>
-    <t>Subdirector de Servicios Administrativos</t>
-  </si>
-  <si>
-    <t>Artículo 32</t>
-  </si>
-  <si>
-    <t>3E8E0867003117F82EF811AB29552A44</t>
-  </si>
-  <si>
-    <t>Director Administrativo</t>
-  </si>
-  <si>
-    <t>Artículo 31</t>
-  </si>
-  <si>
-    <t>EC6F715CF80D00F10DF48085BA24280B</t>
-  </si>
-  <si>
-    <t>Dirección de  Plantel 20 Ixtenco</t>
-  </si>
-  <si>
-    <t>Director del Plantel 20 Ixtenco</t>
-  </si>
-  <si>
-    <t>3D5188084FF89DE018E69F25E1E9C399</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 19 Xaloztoc</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 19 Xaloztoc</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 19 Xaloztoc</t>
-  </si>
-  <si>
-    <t>213433AC83A44904DA1DF927AB9453D9</t>
-  </si>
-  <si>
-    <t>Director del Plantel 19 Xaloztoc</t>
-  </si>
-  <si>
-    <t>759F98F6DCE338502A16B95988FCB308</t>
-  </si>
-  <si>
-    <t>Departamento de actividades deportivas</t>
-  </si>
-  <si>
-    <t>Jefe  de Departamento de actividades deportivas</t>
-  </si>
-  <si>
-    <t>Subdirección de paraescolares</t>
-  </si>
-  <si>
-    <t>A43298484DD86D284544E536570B7781</t>
-  </si>
-  <si>
-    <t>Subdirección de actividades paraescolares</t>
-  </si>
-  <si>
-    <t>Dirección Académica</t>
-  </si>
-  <si>
-    <t>Artículo 29</t>
-  </si>
-  <si>
-    <t>CCA8B8AEA817D45AF5B4096A63F50091</t>
-  </si>
-  <si>
-    <t>Departamento de Control Escolar</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Control Escolar</t>
-  </si>
-  <si>
-    <t>Subdirección de Servicios Escolares</t>
-  </si>
-  <si>
-    <t>Artículo 27</t>
-  </si>
-  <si>
-    <t>4BB02C8129D4D49BE412DF4843936768</t>
-  </si>
-  <si>
-    <t>Subdirector de Servicios Escolares</t>
-  </si>
-  <si>
-    <t>Artículo 26</t>
-  </si>
-  <si>
-    <t>36B08E44FFE47C210339D9DF1CD646C2</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 18 Atltzayanca</t>
-  </si>
-  <si>
-    <t>Director del Plantel 18 Altzayanca</t>
-  </si>
-  <si>
-    <t>B95B2B5C75BA92C15BF2898E36F95F0B</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 17 Cuapiaxtla</t>
-  </si>
-  <si>
-    <t>Director del Plantel 17 Cuapiaxtla</t>
-  </si>
-  <si>
-    <t>30E93D2C79BE8850FF45BF387E7D9E49</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativa del Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>Subdirector Administrativo del Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>4531BFFBD87018335FDE7DBDDB56BB96</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>540E98ACA0D753BBED03D1D27E119C7E</t>
-  </si>
-  <si>
-    <t>Departamento de Planes y Programas de Estudio</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Planes y Programas de Estudio</t>
-  </si>
-  <si>
-    <t>Subdirección de Seguimiento Académico</t>
-  </si>
-  <si>
-    <t>Artículo 22</t>
-  </si>
-  <si>
-    <t>F3C13073E6F5BA75AAA3FE8705470751</t>
-  </si>
-  <si>
-    <t>Departamento de Bibliotecas y Laboratorio</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Bibliotecas y Laboratorio</t>
-  </si>
-  <si>
-    <t>Artículo 24</t>
-  </si>
-  <si>
-    <t>E489E7F2D2A9264EBC39DD7F1C4CF8B2</t>
-  </si>
-  <si>
-    <t>Departamento de Formación y Desarrollo Docente</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Formación y Desarrollo Docente</t>
-  </si>
-  <si>
-    <t>Artículo 23</t>
-  </si>
-  <si>
-    <t>C8B9715417735C026321677FD9B0FDB8</t>
-  </si>
-  <si>
-    <t>Jefatura de Materia</t>
-  </si>
-  <si>
-    <t>Jefe de materia</t>
-  </si>
-  <si>
-    <t>Artículo 25</t>
-  </si>
-  <si>
-    <t>02801C6029AF9459EDA11EFF05EE6043</t>
-  </si>
-  <si>
-    <t>Director del Plantel 02 Huamantla</t>
-  </si>
-  <si>
-    <t>06927F0DCFAD1C47CCB7DBDA5EF63482</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona IV</t>
-  </si>
-  <si>
-    <t>Coordinador Sectorial Zona IV</t>
-  </si>
-  <si>
-    <t>D7512CD140E2234FA017080417FE0CD8</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 15 Hueyotlipan</t>
-  </si>
-  <si>
-    <t>Director del Plantel 15 Hueyotlipan</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona III/ Dirección General</t>
-  </si>
-  <si>
-    <t>DC9DC53EF88016742DFB7A6028EC7F4E</t>
-  </si>
-  <si>
-    <t>Subdirección Plantel 12 Santa Cruz</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 12 Santa Cruz</t>
-  </si>
-  <si>
-    <t>3C4AD92F6207DC431479D4A0FD4CE22F</t>
-  </si>
-  <si>
-    <t>Subdirector de Seguimiento Académico</t>
-  </si>
-  <si>
-    <t>Artículo 21</t>
-  </si>
-  <si>
-    <t>88F73819C38566AB0D8407F15C2C3295</t>
-  </si>
-  <si>
-    <t>Departamento de Planeación y Evaluación Institucional</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Planeación y Evaluación Institucional</t>
-  </si>
-  <si>
-    <t>Artículo 18</t>
-  </si>
-  <si>
-    <t>C6CEFA94182B5BA03CC117865D808775</t>
-  </si>
-  <si>
-    <t>Subdirección de Planeación y Evaluación Institucional</t>
-  </si>
-  <si>
-    <t>Subdirector de Planeación y Evaluación Institucional</t>
-  </si>
-  <si>
-    <t>Artículo 17</t>
-  </si>
-  <si>
-    <t>B69B60B2CE86459D62C8D902FF2353C0</t>
-  </si>
-  <si>
-    <t>Departamento Jurídico</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento Jurídico</t>
-  </si>
-  <si>
-    <t>Subdirección Jurídica</t>
-  </si>
-  <si>
-    <t>Artículo 16</t>
-  </si>
-  <si>
-    <t>2350B19451E96EA1A96ADC4406790EF5</t>
-  </si>
-  <si>
-    <t>Director del Plantel 12 Santa Cruz</t>
-  </si>
-  <si>
-    <t>D19C4DEFD6A6F61039CC3FAB3E4B210B</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 10 Apizaco</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 10 Apizaco</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 10 Apizaco</t>
-  </si>
-  <si>
-    <t>4E2DEBDB6C0B4456FAD3E051F8809EAE</t>
-  </si>
-  <si>
-    <t>Director del Plantel 10 Apizaco</t>
-  </si>
-  <si>
-    <t>73B2CB82C269F962C8B44E59C9CF06AE</t>
-  </si>
-  <si>
-    <t>Subdirector Jurídico</t>
-  </si>
-  <si>
-    <t>Artículo 15</t>
-  </si>
-  <si>
-    <t>56C7340F1B4F30CEA79C713C993DCD7A</t>
-  </si>
-  <si>
-    <t>Departamento de Información y Relaciones Públicas</t>
-  </si>
-  <si>
-    <t>Jefe de Departamento de Información y Relaciones Públicas</t>
-  </si>
-  <si>
-    <t>Artículo 19</t>
-  </si>
-  <si>
-    <t>A5BFB93B515D9B1BC2AE5B5A53DAB11C</t>
-  </si>
-  <si>
-    <t>Unidad de Control Interno</t>
-  </si>
-  <si>
-    <t>Contralor Interno</t>
-  </si>
-  <si>
-    <t>Contralor Interno del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Artículo 52</t>
-  </si>
-  <si>
-    <t>6D905615BA98628281203A6B46B3513D</t>
-  </si>
-  <si>
-    <t>Secretaría General</t>
-  </si>
-  <si>
-    <t>Secretario General del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>AE1A95FC02773D1F0B8CC759A9EF0D09</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 09 Tlaxco</t>
-  </si>
-  <si>
-    <t>Director del Plantel 09 Tlaxco</t>
-  </si>
-  <si>
-    <t>5F16F1F91B75132E9D3B4DDB71E69D75</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 07 Buenavista</t>
-  </si>
-  <si>
-    <t>Director del Plantel 07 Buenavista</t>
-  </si>
-  <si>
-    <t>91F5F3D3C4AC1EBFF25717A2D7FA3E1A</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 03 Calpulalpan</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 03 Calpulalpan</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 03 Calpulalpan</t>
-  </si>
-  <si>
-    <t>A8CAC0B77B621DC7982D0F1F5088C2FC</t>
+    <t>Dirección del Plantel 04 Chiautempan</t>
+  </si>
+  <si>
+    <t>Director del Plantel 04 Chiautempan</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 04 Chiautempan</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 04 Chiautempan</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativo del Plantel 04 Chiautempan</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativo del Plantel 04 Chuiautempan</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>Director del Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>Director del Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativo del Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 21 Ayometla</t>
+  </si>
+  <si>
+    <t>Director del Plantel 21 Ayometla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 22 Texoloc</t>
+  </si>
+  <si>
+    <t>Director del Plantel 22 Texoloc</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 05 Panzacola</t>
+  </si>
+  <si>
+    <t>Director del Plantel 05 Panzacola</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 05 Panzacola</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 05 Panzacola</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 05 Panzacola</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativo del Plantel 05 Panzacola</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 08 Ixtacuixtla</t>
+  </si>
+  <si>
+    <t>Director del Plantel 08 Ixtacuixtla</t>
+  </si>
+  <si>
+    <t>Subdirección del Plantel 08 Ixtacuixtla</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 08 Ixtacuixtla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 13 Papalotla</t>
+  </si>
+  <si>
+    <t>Director de Plante 13 Papalotla</t>
+  </si>
+  <si>
+    <t>Subdirección del Plantel 13 Papalotla</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 13 Papalotla</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Director del Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Subdirector Académico del Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Subdirección Administrativa del Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Subdirector Administrativo del Plantel 14 Nativitas</t>
+  </si>
+  <si>
+    <t>Dirección del Plantel 16 Teolocholco</t>
+  </si>
+  <si>
+    <t>Director del Plantel 16 Teolocholco</t>
+  </si>
+  <si>
+    <t>Subdirección Académica del Plantel 16 Teolocholco</t>
+  </si>
+  <si>
+    <t>Subdirector del Plantel 16 Teolocholco</t>
+  </si>
+  <si>
+    <t>89F6602314351A88D02073673D221946</t>
+  </si>
+  <si>
+    <t>01/10/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
+  </si>
+  <si>
+    <t>12/01/2024</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de octubre de 2023 al 31 de diciembre de 2023, en el Colegio de Bachilleres del Estado de Tlaxcala, de acuerdo a la norma que establece atribuciones responsabilidades y/o funciones, estos son nombrados y se rigen de acuerdo los articulos 16, 18 y 30 de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala y al articulo 21 fraccion VIII del Reglamento General de la Ley que Crea el Colegio de Bachilleres del Estado de Tlaxcala.  El Director como autortidad superior jerarquica de Plantel, tiene la facultad de asignar las funciones a realizar a los subdirectores, con relación a los prestadores de servicios profesionales que formen parte de la estructura orgánica, este sujeto obligado no genero información respecto a este tema.</t>
+  </si>
+  <si>
+    <t>7A62E7607A145C7D4DA595232FED61A8</t>
   </si>
   <si>
     <t>Subdirección Administrativa del Plantel 03 Calpulalpan</t>
@@ -709,253 +772,256 @@
     <t>Subdirector Administrativo del Plantel 03 Calpulalpan</t>
   </si>
   <si>
-    <t>DB37538ABEB436D05CEB673362DE00A4</t>
-  </si>
-  <si>
-    <t>Director General</t>
-  </si>
-  <si>
-    <t>Director General del Colegio de Bachilleres del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Junta Directiva - Gobierno del Estado de Tlaxcala</t>
-  </si>
-  <si>
-    <t>Artículo 10</t>
-  </si>
-  <si>
-    <t>B57BE21A8FE699C1DAD54FC1BBE19272</t>
-  </si>
-  <si>
-    <t>Director del Plantel 03 Calpulalpan</t>
-  </si>
-  <si>
-    <t>2A3D9E54CC37FBF1A485C85032D48F78</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona III</t>
-  </si>
-  <si>
-    <t>Coordinador Sectorial Zona III</t>
-  </si>
-  <si>
-    <t>EE273914545D7E81BC6ADFF4ED909CEE</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 23 San Pablo</t>
-  </si>
-  <si>
-    <t>Director del Plantel 23 San Pablo</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona II/ Dirección General</t>
-  </si>
-  <si>
-    <t>23F293320AC7D2E06F4CEB38D0BC67E3</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 16 Teolocholco</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 16 Teolocholco</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 16 Teolocholco</t>
-  </si>
-  <si>
-    <t>8400C56A1A5CE35FAE2C7E4792648289</t>
-  </si>
-  <si>
-    <t>Director del Plantel 16 Teolocholco</t>
-  </si>
-  <si>
-    <t>42E130DF450FC85F24814EC5E65CD39A</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativa del Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>Subdirector Administrativo del Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>985DB9DFB274FB663E2B917DEF55C969</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>C899085CEA5EF3B8FBC9FA43BFCF2871</t>
-  </si>
-  <si>
-    <t>Director del Plantel 14 Nativitas</t>
-  </si>
-  <si>
-    <t>AD1A0E6E93A1623E95B4C04F23C32A9E</t>
-  </si>
-  <si>
-    <t>Subdirección del Plantel 13 Papalotla</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 13 Papalotla</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 13 Papalotla</t>
-  </si>
-  <si>
-    <t>39D653215DDC5EBA2E54AC0152F2EE44</t>
-  </si>
-  <si>
-    <t>Director de Plante 13 Papalotla</t>
-  </si>
-  <si>
-    <t>6242D97DA4EA173240789D451B75EF57</t>
-  </si>
-  <si>
-    <t>Subdirección del Plantel 08 Ixtacuixtla</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 08 Ixtacuixtla</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 08 Ixtacuixtla</t>
-  </si>
-  <si>
-    <t>20D018BE64517D7D534A672F337D2DFC</t>
-  </si>
-  <si>
-    <t>Director del Plantel 08 Ixtacuixtla</t>
-  </si>
-  <si>
-    <t>56D15A09C258471ED31F0B5562937AC1</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 05 Panzacola</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 05 Panzacola</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 05 Panzacola</t>
-  </si>
-  <si>
-    <t>4C4CF14DD4F0BF5D7409A79E6FC56580</t>
-  </si>
-  <si>
-    <t>Director del Plantel 05 Panzacola</t>
-  </si>
-  <si>
-    <t>BC941CDD6D4E43D7A228FF77B8308F5F</t>
-  </si>
-  <si>
-    <t>Coordinación Sectorial Zona II</t>
-  </si>
-  <si>
-    <t>Coordinador Sectorial Zona II</t>
-  </si>
-  <si>
-    <t>FF83B74EB63DC8D97D3D4221207A286C</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 22 Texoloc</t>
-  </si>
-  <si>
-    <t>Director del Plantel 22 Texoloc</t>
-  </si>
-  <si>
-    <t>BB325D70C6CFBA45D04EF5944E78433E</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 21 Ayometla</t>
-  </si>
-  <si>
-    <t>Director del Plantel 21 Ayometla</t>
-  </si>
-  <si>
-    <t>3689D26BD2F3196763C3C524A3223EA6</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 11 Panotla</t>
-  </si>
-  <si>
-    <t>Subdirector Administrativo del Plantel 11 Panotla</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 11 Panotla</t>
-  </si>
-  <si>
-    <t>F36C0F192A1401A62E7975E0AD60D504</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativa del Plantel 11 Panotla</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 11 Panotla</t>
-  </si>
-  <si>
-    <t>789707756824ED7C425E5CF3B826DEB6</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>Subdirector Administrativo del Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>A52CA130F66F8F5FEC79F7F55CC954B4</t>
+    <t>0B70BE7D43C24331DAD9DCBB39418963</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de octubre de 2023 al 31 de diciembre de 2023, en el Colegio de Bachilleres del Estado de Tlaxcala, es facultad del Director General  proponer ante la Junta Directiva las candidaturas para ocupar las Direcciones de las unidades administrativas y de los planteles, motivo por el cual no se tiene ninguna norma establecida con los requerimientos del puesto  para cubrir  un perfil Directivo. De igual forma este Colegio de Bachilleres del Estado de Tlaxcala, no cuenta con prestadores de servicios profesionales que formen parte de la estructura orgánica, por lo tanto no hay información que reportar.</t>
+  </si>
+  <si>
+    <t>627A03A02B5A26D2E5361399F48EBC7D</t>
+  </si>
+  <si>
+    <t>E4E354BD0EF29231DBE79B200854FDD1</t>
+  </si>
+  <si>
+    <t>53409AAE8D46FC4F7DEE38972B960DBA</t>
+  </si>
+  <si>
+    <t>A0D4F85F8419DBF76B6BF3AE638B6D58</t>
+  </si>
+  <si>
+    <t>53DD53B9BBD918A693D1395A5DF76BBD</t>
+  </si>
+  <si>
+    <t>42074A58D90FBDCB925A7683A83B9E41</t>
+  </si>
+  <si>
+    <t>A3AC9BF94A4B22C01A3616E52D57BC81</t>
+  </si>
+  <si>
+    <t>B34D494DD027E1B68699BFD467EA3B29</t>
+  </si>
+  <si>
+    <t>82D455817C1D8388EC5870250AEDEF77</t>
+  </si>
+  <si>
+    <t>D9C73EFB254E4A15380B5171F527E662</t>
+  </si>
+  <si>
+    <t>004AC930145CACD7C40F9FF031B68FDE</t>
+  </si>
+  <si>
+    <t>A0C847E680DFC0EECAA3E4609C8E1082</t>
+  </si>
+  <si>
+    <t>A673C356F8F69ABC75A58C3E35EDBA7C</t>
+  </si>
+  <si>
+    <t>C91FFABA12C3026C5600DE816D0BC0F1</t>
+  </si>
+  <si>
+    <t>93B378F6D4B884E0FFD781864D7E5D0E</t>
+  </si>
+  <si>
+    <t>EFD9C96DB3E48815C0DB39C4184267E1</t>
+  </si>
+  <si>
+    <t>151EC06CAB2249E6990584E5C34726BE</t>
+  </si>
+  <si>
+    <t>85EB7F814F2D47B0EA854F5345777515</t>
+  </si>
+  <si>
+    <t>9920CB06ED06E11ED25AB0CAF5FAF67B</t>
+  </si>
+  <si>
+    <t>90AD2D20D3B9DE67776202133BDA6AD9</t>
+  </si>
+  <si>
+    <t>74A2E222E35AF98BC72CC497DCF3D12D</t>
+  </si>
+  <si>
+    <t>6B79FC2C5D48C9DE6756E698E949BC65</t>
+  </si>
+  <si>
+    <t>1978C79AC15C3AADF88EBD5806A1C134</t>
+  </si>
+  <si>
+    <t>8F31B83EA42F7FAD734C1522DF870299</t>
+  </si>
+  <si>
+    <t>DC6119EA24A54473049493076473D4ED</t>
+  </si>
+  <si>
+    <t>963F9F98F40CBBBB5F49A421937067E3</t>
+  </si>
+  <si>
+    <t>8D262C1126E16CFFCBACBA2BC3F800CF</t>
+  </si>
+  <si>
+    <t>Subdirector Academico del Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>6A7DD445844DDECAD761DF5061BAD6D2</t>
   </si>
   <si>
     <t>Subdirección Administrativa del Plantel 06 Contla</t>
   </si>
   <si>
-    <t>Subdirector Académico del Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>FA31F0E2B2371F197EFFECC4C9F90CFA</t>
-  </si>
-  <si>
-    <t>Director del Plantel 06 Contla</t>
-  </si>
-  <si>
-    <t>CB1E24120469C7AF83B3D8707C468805</t>
-  </si>
-  <si>
-    <t>Subdirección Administrativo del Plantel 04 Chiautempan</t>
-  </si>
-  <si>
-    <t>Subdirector Administrativo del Plantel 04 Chuiautempan</t>
-  </si>
-  <si>
-    <t>Dirección del Plantel 04 Chiautempan</t>
-  </si>
-  <si>
-    <t>E2807D44C5C8A76921A70D099E46A8B9</t>
-  </si>
-  <si>
-    <t>Subdirección Académica del Plantel 04 Chiautempan</t>
-  </si>
-  <si>
-    <t>Subdirector Académico del Plantel 04 Chiautempan</t>
-  </si>
-  <si>
-    <t>F2C5296C8A085F71AF9CAB01B610FBF5</t>
-  </si>
-  <si>
-    <t>Director del Plantel 04 Chiautempan</t>
+    <t>Subdirectora Administrativa del Plantel 06 Contla</t>
+  </si>
+  <si>
+    <t>58734578E7FA2DC86496E13D4AD6BB42</t>
+  </si>
+  <si>
+    <t>E5D6C807EA93F53E69746F265D8F2C26</t>
+  </si>
+  <si>
+    <t>B5A170925E164A73361C70FF589F787A</t>
+  </si>
+  <si>
+    <t>Subdirectora Académica del Plantel 11 Panotla</t>
+  </si>
+  <si>
+    <t>B36FBE42C5C7A798033D1B53B2646FF7</t>
+  </si>
+  <si>
+    <t>809787680D03EA5A5BD1EFC0AD004C1F</t>
+  </si>
+  <si>
+    <t>4B97070E4027F9657343FBD79C4DDCDD</t>
+  </si>
+  <si>
+    <t>D6BA55E8DA975480442B5A9972BFEE7F</t>
+  </si>
+  <si>
+    <t>7BE0C2CCD45E98EC52FE536A3AAA1F3D</t>
+  </si>
+  <si>
+    <t>D6FF4FAB2C0D5604E8C2852BBA762907</t>
+  </si>
+  <si>
+    <t>A1D8D26CE18D60868582671F6BD8CA07</t>
+  </si>
+  <si>
+    <t>AA8EC7AAB2FAC0CA9549D120B47F22E7</t>
+  </si>
+  <si>
+    <t>0DD10FB3952FF52E598B9C578EADC121</t>
+  </si>
+  <si>
+    <t>9C47D930BD0009F4D222142BB4EA580F</t>
+  </si>
+  <si>
+    <t>576F7EEF6CFF29A73E29B896E4ACB506</t>
+  </si>
+  <si>
+    <t>12E061CE287DE11B8B80BEB881F65767</t>
+  </si>
+  <si>
+    <t>AE37A0A62A37F1C6391D42EF1FE0911F</t>
+  </si>
+  <si>
+    <t>406568BE25D840C1EDB8C97EA1C1CD21</t>
+  </si>
+  <si>
+    <t>E65B417ED13B6B67D928BA5AD40227EE</t>
+  </si>
+  <si>
+    <t>D4C2154C0CC2FCC0E2478C9E029CF8C1</t>
+  </si>
+  <si>
+    <t>090DAE256C798D3386AD7997DD832BA5</t>
+  </si>
+  <si>
+    <t>DD0450E711408B559FE23D751D3C2C47</t>
+  </si>
+  <si>
+    <t>37D80BF43646750A4DB27CFB1EC80B33</t>
+  </si>
+  <si>
+    <t>B7B28D31D9A14081CB6B3015E3CBD715</t>
+  </si>
+  <si>
+    <t>DC1CE64F096164C796DC9E9F2E987DE1</t>
+  </si>
+  <si>
+    <t>443E9D562E527745903D5086447C16AA</t>
+  </si>
+  <si>
+    <t>6093B6A591E88873B1C0C56757DA7797</t>
+  </si>
+  <si>
+    <t>C117ED5B2F6FC58BB29C4117C85AE51F</t>
+  </si>
+  <si>
+    <t>B52B5517A45D8A324685F0385F5F121A</t>
+  </si>
+  <si>
+    <t>2D3C6938B29EE3133C06F41FDE6883EC</t>
+  </si>
+  <si>
+    <t>05240A760EEBBB34DFA84AF29B18BE10</t>
+  </si>
+  <si>
+    <t>83E14012DDC6756271EA578E8C40D73C</t>
+  </si>
+  <si>
+    <t>8F83825B1B44BC189C62956D5D9865DB</t>
+  </si>
+  <si>
+    <t>AE1B8A4BED873A99EBB52B3CA0C708A2</t>
+  </si>
+  <si>
+    <t>FAFB8DEADB21725919F49D9C475139F1</t>
+  </si>
+  <si>
+    <t>C2EB7158D7738966B22F969F46326B05</t>
+  </si>
+  <si>
+    <t>A020B6B97B9468E3D79CBB2C7AEA8E08</t>
+  </si>
+  <si>
+    <t>7A96A364F7930709C670AD217492765F</t>
+  </si>
+  <si>
+    <t>43A7E3632132AC18D3F056D39D0130CA</t>
+  </si>
+  <si>
+    <t>E271F852B9DF651DB20A5C130012AD71</t>
+  </si>
+  <si>
+    <t>33F380770A807B086D78EC0A06F6E44B</t>
+  </si>
+  <si>
+    <t>751AA0721180D1ADF02CBF4ED6981C00</t>
+  </si>
+  <si>
+    <t>919354687562319FF57D101F3340624D</t>
+  </si>
+  <si>
+    <t>4C6BAC951633DD7EAB50945A74960010</t>
+  </si>
+  <si>
+    <t>22208864D8F156D0907F209292A11139</t>
+  </si>
+  <si>
+    <t>340077059FBAFAE02A6377514AD24220</t>
+  </si>
+  <si>
+    <t>DF2BCAF230ED17A1CA54C39C83208817</t>
+  </si>
+  <si>
+    <t>A6D6EA410639417EF9FA9EF5D5088652</t>
+  </si>
+  <si>
+    <t>7D6088BC28F50139AD53E78130FFE8A1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1051,6 +1117,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -1066,44 +1135,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1131,14 +1200,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1166,6 +1252,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1177,185 +1280,161 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P81"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.42578125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="37" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="51.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="56.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="60.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="111.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="55.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="60.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="89.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="95" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="47.140625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -1563,3702 +1642,3952 @@
     </row>
     <row r="8" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>242</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>247</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>58</v>
+        <v>248</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>59</v>
+        <v>249</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>65</v>
+        <v>252</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="I11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="K11" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>71</v>
+        <v>253</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>77</v>
+        <v>254</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>255</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>86</v>
+        <v>256</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>87</v>
+        <v>64</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>91</v>
+        <v>257</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>95</v>
+        <v>258</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>99</v>
+        <v>259</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>103</v>
+        <v>260</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>106</v>
+        <v>261</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>108</v>
+        <v>55</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>109</v>
+        <v>262</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>110</v>
+        <v>59</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>112</v>
+        <v>263</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>115</v>
+        <v>264</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="F23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>119</v>
+        <v>265</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>121</v>
+        <v>266</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>125</v>
+        <v>267</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>129</v>
+        <v>268</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>134</v>
+        <v>269</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>137</v>
+        <v>270</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>140</v>
+        <v>271</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>143</v>
+        <v>272</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>144</v>
+        <v>196</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="32" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>147</v>
+        <v>273</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>150</v>
+        <v>274</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>151</v>
+        <v>200</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>154</v>
+        <v>68</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>155</v>
+        <v>275</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>156</v>
+        <v>202</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>159</v>
+        <v>276</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>160</v>
+        <v>204</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>161</v>
+        <v>205</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>153</v>
+        <v>200</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>162</v>
+        <v>55</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>163</v>
+        <v>277</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>164</v>
+        <v>206</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>166</v>
+        <v>68</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>146</v>
+        <v>208</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>168</v>
+        <v>279</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>94</v>
+        <v>206</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>169</v>
+        <v>280</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>170</v>
+        <v>281</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>171</v>
+        <v>282</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>69</v>
+        <v>206</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>172</v>
+        <v>283</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>176</v>
+        <v>284</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>177</v>
+        <v>211</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>177</v>
+        <v>213</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>179</v>
+        <v>285</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>153</v>
+        <v>212</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>180</v>
+        <v>286</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>127</v>
+        <v>209</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>181</v>
+        <v>55</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>182</v>
+        <v>287</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>184</v>
+        <v>215</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>186</v>
+        <v>288</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>189</v>
+        <v>68</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>190</v>
+        <v>289</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>193</v>
+        <v>76</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>194</v>
+        <v>68</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>195</v>
+        <v>290</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>175</v>
+        <v>218</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>197</v>
+        <v>291</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>201</v>
+        <v>292</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>200</v>
+        <v>224</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>175</v>
+        <v>76</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>203</v>
+        <v>293</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>69</v>
+        <v>224</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>205</v>
+        <v>55</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>206</v>
+        <v>294</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>209</v>
+        <v>68</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>210</v>
+        <v>295</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>212</v>
+        <v>59</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>69</v>
+        <v>228</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>214</v>
+        <v>55</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>215</v>
+        <v>296</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>216</v>
+        <v>65</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>221</v>
+        <v>298</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>224</v>
+        <v>299</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="F54" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I54" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G54" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J54" s="2" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>228</v>
+        <v>300</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>231</v>
+        <v>301</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>232</v>
+        <v>65</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>233</v>
+        <v>75</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>234</v>
+        <v>76</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>235</v>
+        <v>68</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>236</v>
+        <v>302</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H57" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="I57" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>238</v>
+        <v>303</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>239</v>
+        <v>81</v>
       </c>
       <c r="F58" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="G58" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="I58" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>241</v>
+        <v>304</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>242</v>
+        <v>182</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>243</v>
+        <v>183</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>64</v>
+        <v>185</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>245</v>
+        <v>305</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>246</v>
+        <v>52</v>
       </c>
       <c r="F60" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I60" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G60" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J60" s="2" t="s">
-        <v>53</v>
+        <v>187</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>248</v>
+        <v>177</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>250</v>
+        <v>178</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>64</v>
+        <v>179</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="P62" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J62" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N62" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="O62" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="P62" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="F63" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I63" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G63" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J63" s="2" t="s">
-        <v>53</v>
+        <v>181</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>258</v>
+        <v>309</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>254</v>
+        <v>188</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>259</v>
+        <v>189</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>244</v>
+        <v>184</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>64</v>
+        <v>190</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H65" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F65" s="2" t="s">
+      <c r="I65" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G65" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J65" s="2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>263</v>
+        <v>193</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>265</v>
+        <v>194</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>244</v>
+        <v>195</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>266</v>
+        <v>312</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>267</v>
+        <v>149</v>
       </c>
       <c r="F67" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I67" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G67" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J67" s="2" t="s">
-        <v>53</v>
+        <v>151</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>270</v>
+        <v>313</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>269</v>
+        <v>152</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>271</v>
+        <v>153</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>244</v>
+        <v>146</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>273</v>
+        <v>155</v>
       </c>
       <c r="F69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I69" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G69" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J69" s="2" t="s">
-        <v>53</v>
+        <v>157</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>276</v>
+        <v>315</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>275</v>
+        <v>158</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>277</v>
+        <v>159</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>244</v>
+        <v>136</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>64</v>
+        <v>160</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>278</v>
+        <v>316</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>279</v>
+        <v>162</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>280</v>
+        <v>163</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>70</v>
+        <v>161</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="72" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>282</v>
+        <v>164</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>283</v>
+        <v>164</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>68</v>
+        <v>136</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>64</v>
+        <v>165</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>284</v>
+        <v>318</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>285</v>
+        <v>166</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>286</v>
+        <v>167</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>64</v>
+        <v>138</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>287</v>
+        <v>319</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="H74" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="F74" s="2" t="s">
+      <c r="I74" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G74" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J74" s="2" t="s">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>291</v>
+        <v>320</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>46</v>
+        <v>243</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>47</v>
+        <v>244</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>292</v>
+        <v>171</v>
       </c>
       <c r="F75" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I75" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J75" s="2" t="s">
-        <v>53</v>
+        <v>173</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="F76" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D76" s="2" t="s">
+      <c r="G76" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F76" s="2" t="s">
+      <c r="H76" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I76" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G76" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J76" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>298</v>
+        <v>322</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>299</v>
-      </c>
       <c r="F77" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>300</v>
+        <v>54</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>297</v>
+        <v>45</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>297</v>
-      </c>
       <c r="F78" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>302</v>
+        <v>57</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>56</v>
+        <v>246</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H79" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F79" s="2" t="s">
+      <c r="I79" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G79" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J79" s="2" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F80" s="2" t="s">
+      <c r="I80" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J80" s="2" t="s">
-        <v>53</v>
+        <v>127</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H81" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="I81" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>55</v>
+        <v>245</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>56</v>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="P86" s="2" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
